--- a/Tools/Luban/DataTables/Datas/UIWindow.xlsx
+++ b/Tools/Luban/DataTables/Datas/UIWindow.xlsx
@@ -1073,7 +1073,7 @@
         <x:v>Inkspell 主界面</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>UIInkspellMainWindow</x:v>
+        <x:v>MainWindow</x:v>
       </x:c>
       <x:c r="E5" t="n">
         <x:v>0</x:v>
